--- a/cadastrar.xlsx
+++ b/cadastrar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gitlocal\protheus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A14F2EA-E760-4B3C-A136-708E9736D8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7BCE3F-7BFF-4C0D-BC0D-44ED8B3CED23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1590" yWindow="150" windowWidth="18900" windowHeight="10800" xr2:uid="{1589334F-D7EF-4C27-A54A-7D2B83ACDBA2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{1589334F-D7EF-4C27-A54A-7D2B83ACDBA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="150">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -474,6 +474,21 @@
   </si>
   <si>
     <t>8000ZE</t>
+  </si>
+  <si>
+    <t>COD_CONTATO</t>
+  </si>
+  <si>
+    <t>CLASSIFIC</t>
+  </si>
+  <si>
+    <t>OCORRENCIA</t>
+  </si>
+  <si>
+    <t>MEMO</t>
+  </si>
+  <si>
+    <t>ACESSORIOS</t>
   </si>
 </sst>
 </file>
@@ -522,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -550,6 +565,21 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -885,11 +915,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7600A1C-8D91-4C3A-A5DE-920816BE31C1}">
-  <dimension ref="A1:T100"/>
+  <dimension ref="A1:Y100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" style="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
@@ -907,13 +937,15 @@
     <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.140625" customWidth="1"/>
+    <col min="22" max="22" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -970,12 +1002,27 @@
       <c r="T1" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -1032,11 +1079,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -1093,11 +1140,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -1154,11 +1201,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C5" s="11" t="s">
@@ -1215,11 +1262,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C6" s="11" t="s">
@@ -1276,11 +1323,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C7" s="11" t="s">
@@ -1337,11 +1384,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C8" s="11" t="s">
@@ -1398,11 +1445,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C9" s="11" t="s">
@@ -1459,11 +1506,11 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -1520,11 +1567,11 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -1581,11 +1628,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -1642,11 +1689,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C13" s="11" t="s">
@@ -1703,11 +1750,11 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C14" s="11" t="s">
@@ -1764,11 +1811,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C15" s="11" t="s">
@@ -1825,11 +1872,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C16" s="11" t="s">
@@ -1890,7 +1937,7 @@
       <c r="A17" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C17" s="11" t="s">
@@ -1951,7 +1998,7 @@
       <c r="A18" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -2012,7 +2059,7 @@
       <c r="A19" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C19" s="11" t="s">
@@ -2073,7 +2120,7 @@
       <c r="A20" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C20" s="11" t="s">
@@ -2134,7 +2181,7 @@
       <c r="A21" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C21" s="11" t="s">
@@ -2195,7 +2242,7 @@
       <c r="A22" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C22" s="11" t="s">
@@ -2256,7 +2303,7 @@
       <c r="A23" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C23" s="11" t="s">
@@ -2317,7 +2364,7 @@
       <c r="A24" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C24" s="11" t="s">
@@ -2378,7 +2425,7 @@
       <c r="A25" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C25" s="11" t="s">
@@ -2439,7 +2486,7 @@
       <c r="A26" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C26" s="11" t="s">
@@ -2500,7 +2547,7 @@
       <c r="A27" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C27" s="11" t="s">
@@ -2561,7 +2608,7 @@
       <c r="A28" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C28" s="11" t="s">
@@ -2622,7 +2669,7 @@
       <c r="A29" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C29" s="11" t="s">
@@ -2683,7 +2730,7 @@
       <c r="A30" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C30" s="11" t="s">
@@ -2744,7 +2791,7 @@
       <c r="A31" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C31" s="11" t="s">
@@ -2805,7 +2852,7 @@
       <c r="A32" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C32" s="11" t="s">
@@ -2866,7 +2913,7 @@
       <c r="A33" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C33" s="11" t="s">
@@ -2927,7 +2974,7 @@
       <c r="A34" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C34" s="11" t="s">
@@ -2988,7 +3035,7 @@
       <c r="A35" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C35" s="11" t="s">
@@ -3049,7 +3096,7 @@
       <c r="A36" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C36" s="11" t="s">
@@ -3110,7 +3157,7 @@
       <c r="A37" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C37" s="11" t="s">
@@ -3171,7 +3218,7 @@
       <c r="A38" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C38" s="11" t="s">
@@ -3232,7 +3279,7 @@
       <c r="A39" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C39" s="11" t="s">
@@ -3293,7 +3340,7 @@
       <c r="A40" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C40" s="11" t="s">
@@ -3354,7 +3401,7 @@
       <c r="A41" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C41" s="11" t="s">
@@ -3415,7 +3462,7 @@
       <c r="A42" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C42" s="11" t="s">
@@ -3476,7 +3523,7 @@
       <c r="A43" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C43" s="11" t="s">
@@ -3537,7 +3584,7 @@
       <c r="A44" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C44" s="11" t="s">
@@ -3598,7 +3645,7 @@
       <c r="A45" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C45" s="11" t="s">
@@ -3659,7 +3706,7 @@
       <c r="A46" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C46" s="11" t="s">
@@ -3720,7 +3767,7 @@
       <c r="A47" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C47" s="11" t="s">
@@ -3781,7 +3828,7 @@
       <c r="A48" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C48" s="11" t="s">
@@ -3842,7 +3889,7 @@
       <c r="A49" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C49" s="11" t="s">
@@ -3903,7 +3950,7 @@
       <c r="A50" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C50" s="11" t="s">
@@ -3964,7 +4011,7 @@
       <c r="A51" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="15" t="s">
         <v>136</v>
       </c>
       <c r="C51" s="11" t="s">
@@ -4025,7 +4072,7 @@
       <c r="A52" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="15">
         <v>11</v>
       </c>
       <c r="C52" s="11" t="s">
@@ -4086,7 +4133,7 @@
       <c r="A53" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="15">
         <v>11</v>
       </c>
       <c r="C53" s="11" t="s">
@@ -4147,7 +4194,7 @@
       <c r="A54" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="15">
         <v>11</v>
       </c>
       <c r="C54" s="11" t="s">
@@ -4208,7 +4255,7 @@
       <c r="A55" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="15">
         <v>11</v>
       </c>
       <c r="C55" s="11" t="s">
@@ -4269,7 +4316,7 @@
       <c r="A56" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="15">
         <v>11</v>
       </c>
       <c r="C56" s="11" t="s">
@@ -4330,7 +4377,7 @@
       <c r="A57" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="15">
         <v>11</v>
       </c>
       <c r="C57" s="11" t="s">
@@ -4391,7 +4438,7 @@
       <c r="A58" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="15">
         <v>11</v>
       </c>
       <c r="C58" s="11" t="s">
@@ -4452,7 +4499,7 @@
       <c r="A59" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="15">
         <v>11</v>
       </c>
       <c r="C59" s="11" t="s">
@@ -4513,7 +4560,7 @@
       <c r="A60" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="15">
         <v>11</v>
       </c>
       <c r="C60" s="11" t="s">
@@ -4574,7 +4621,7 @@
       <c r="A61" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="15">
         <v>11</v>
       </c>
       <c r="C61" s="11" t="s">
@@ -4635,7 +4682,7 @@
       <c r="A62" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="15" t="s">
         <v>139</v>
       </c>
       <c r="C62" s="11" t="s">
@@ -4696,7 +4743,7 @@
       <c r="A63" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="15" t="s">
         <v>139</v>
       </c>
       <c r="C63" s="11" t="s">
@@ -4757,7 +4804,7 @@
       <c r="A64" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="15" t="s">
         <v>139</v>
       </c>
       <c r="C64" s="11" t="s">
@@ -4818,7 +4865,7 @@
       <c r="A65" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="15" t="s">
         <v>139</v>
       </c>
       <c r="C65" s="11" t="s">
@@ -4879,7 +4926,7 @@
       <c r="A66" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="15" t="s">
         <v>139</v>
       </c>
       <c r="C66" s="11" t="s">
@@ -4940,7 +4987,7 @@
       <c r="A67" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="15" t="s">
         <v>139</v>
       </c>
       <c r="C67" s="11" t="s">
@@ -5001,7 +5048,7 @@
       <c r="A68" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="15" t="s">
         <v>139</v>
       </c>
       <c r="C68" s="11" t="s">
@@ -5062,7 +5109,7 @@
       <c r="A69" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="15" t="s">
         <v>139</v>
       </c>
       <c r="C69" s="11" t="s">
@@ -5123,7 +5170,7 @@
       <c r="A70" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="15" t="s">
         <v>139</v>
       </c>
       <c r="C70" s="11" t="s">
@@ -5184,7 +5231,7 @@
       <c r="A71" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="15" t="s">
         <v>139</v>
       </c>
       <c r="C71" s="11" t="s">
@@ -5245,7 +5292,7 @@
       <c r="A72" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C72" s="11" t="s">
@@ -5306,7 +5353,7 @@
       <c r="A73" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C73" s="11" t="s">
@@ -5367,7 +5414,7 @@
       <c r="A74" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C74" s="11" t="s">
@@ -5428,7 +5475,7 @@
       <c r="A75" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C75" s="11" t="s">
@@ -5489,7 +5536,7 @@
       <c r="A76" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C76" s="11" t="s">
@@ -5550,7 +5597,7 @@
       <c r="A77" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C77" s="11" t="s">
@@ -5611,7 +5658,7 @@
       <c r="A78" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C78" s="11" t="s">
@@ -5672,7 +5719,7 @@
       <c r="A79" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C79" s="11" t="s">
@@ -5733,7 +5780,7 @@
       <c r="A80" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C80" s="11" t="s">
@@ -5794,7 +5841,7 @@
       <c r="A81" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C81" s="11" t="s">
@@ -5855,7 +5902,7 @@
       <c r="A82" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B82" s="17" t="s">
         <v>136</v>
       </c>
       <c r="C82" s="11" t="s">
@@ -5916,7 +5963,7 @@
       <c r="A83" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="17" t="s">
         <v>136</v>
       </c>
       <c r="C83" s="11" t="s">
@@ -5977,7 +6024,7 @@
       <c r="A84" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="17" t="s">
         <v>136</v>
       </c>
       <c r="C84" s="11" t="s">
@@ -6038,7 +6085,7 @@
       <c r="A85" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="17" t="s">
         <v>136</v>
       </c>
       <c r="C85" s="11" t="s">
@@ -6099,7 +6146,7 @@
       <c r="A86" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="17" t="s">
         <v>136</v>
       </c>
       <c r="C86" s="11" t="s">
@@ -6160,7 +6207,7 @@
       <c r="A87" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B87" s="17" t="s">
         <v>140</v>
       </c>
       <c r="C87" s="11" t="s">
@@ -6221,7 +6268,7 @@
       <c r="A88" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" s="17" t="s">
         <v>140</v>
       </c>
       <c r="C88" s="11" t="s">
@@ -6282,7 +6329,7 @@
       <c r="A89" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="17" t="s">
         <v>137</v>
       </c>
       <c r="C89" s="11" t="s">
@@ -6343,7 +6390,7 @@
       <c r="A90" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B90" s="17" t="s">
         <v>137</v>
       </c>
       <c r="C90" s="11" t="s">
@@ -6404,7 +6451,7 @@
       <c r="A91" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" s="17" t="s">
         <v>137</v>
       </c>
       <c r="C91" s="11" t="s">
@@ -6465,7 +6512,7 @@
       <c r="A92" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="17" t="s">
         <v>137</v>
       </c>
       <c r="C92" s="11" t="s">
@@ -6526,7 +6573,7 @@
       <c r="A93" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B93" s="17" t="s">
         <v>137</v>
       </c>
       <c r="C93" s="11" t="s">
@@ -6587,7 +6634,7 @@
       <c r="A94" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B94" s="17" t="s">
         <v>137</v>
       </c>
       <c r="C94" s="11" t="s">
@@ -6648,7 +6695,7 @@
       <c r="A95" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B95" s="17" t="s">
         <v>137</v>
       </c>
       <c r="C95" s="11" t="s">
@@ -6709,7 +6756,7 @@
       <c r="A96" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B96" s="17" t="s">
         <v>137</v>
       </c>
       <c r="C96" s="11" t="s">
@@ -6770,7 +6817,7 @@
       <c r="A97" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B97" s="17" t="s">
         <v>137</v>
       </c>
       <c r="C97" s="11" t="s">
@@ -6831,7 +6878,7 @@
       <c r="A98" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B98" s="17" t="s">
         <v>137</v>
       </c>
       <c r="C98" s="11" t="s">
@@ -6890,7 +6937,7 @@
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="10"/>
-      <c r="B99" s="10"/>
+      <c r="B99" s="17"/>
       <c r="C99" s="10"/>
       <c r="D99" s="6"/>
       <c r="E99" s="9"/>
@@ -6912,7 +6959,7 @@
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="10"/>
-      <c r="B100" s="10"/>
+      <c r="B100" s="17"/>
       <c r="C100" s="10"/>
       <c r="D100" s="6"/>
       <c r="E100" s="9"/>

--- a/cadastrar.xlsx
+++ b/cadastrar.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gitlocal\protheus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitlocal\protheus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7BCE3F-7BFF-4C0D-BC0D-44ED8B3CED23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97A763C-9BE4-4281-AB34-04445E67C5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{1589334F-D7EF-4C27-A54A-7D2B83ACDBA2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{1589334F-D7EF-4C27-A54A-7D2B83ACDBA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$AA$98</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="256">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -489,6 +492,324 @@
   </si>
   <si>
     <t>ACESSORIOS</t>
+  </si>
+  <si>
+    <t>NUM_OS</t>
+  </si>
+  <si>
+    <t>025626</t>
+  </si>
+  <si>
+    <t>025627</t>
+  </si>
+  <si>
+    <t>025628</t>
+  </si>
+  <si>
+    <t>025629</t>
+  </si>
+  <si>
+    <t>025630</t>
+  </si>
+  <si>
+    <t>025631</t>
+  </si>
+  <si>
+    <t>025632</t>
+  </si>
+  <si>
+    <t>025633</t>
+  </si>
+  <si>
+    <t>025634</t>
+  </si>
+  <si>
+    <t>025635</t>
+  </si>
+  <si>
+    <t>025636</t>
+  </si>
+  <si>
+    <t>025637</t>
+  </si>
+  <si>
+    <t>025638</t>
+  </si>
+  <si>
+    <t>025639</t>
+  </si>
+  <si>
+    <t>025640</t>
+  </si>
+  <si>
+    <t>025641</t>
+  </si>
+  <si>
+    <t>025642</t>
+  </si>
+  <si>
+    <t>025643</t>
+  </si>
+  <si>
+    <t>025644</t>
+  </si>
+  <si>
+    <t>025645</t>
+  </si>
+  <si>
+    <t>025646</t>
+  </si>
+  <si>
+    <t>025647</t>
+  </si>
+  <si>
+    <t>025648</t>
+  </si>
+  <si>
+    <t>025649</t>
+  </si>
+  <si>
+    <t>025650</t>
+  </si>
+  <si>
+    <t>025651</t>
+  </si>
+  <si>
+    <t>025652</t>
+  </si>
+  <si>
+    <t>025653</t>
+  </si>
+  <si>
+    <t>025654</t>
+  </si>
+  <si>
+    <t>025655</t>
+  </si>
+  <si>
+    <t>025656</t>
+  </si>
+  <si>
+    <t>025657</t>
+  </si>
+  <si>
+    <t>025658</t>
+  </si>
+  <si>
+    <t>025659</t>
+  </si>
+  <si>
+    <t>025660</t>
+  </si>
+  <si>
+    <t>025661</t>
+  </si>
+  <si>
+    <t>025662</t>
+  </si>
+  <si>
+    <t>025663</t>
+  </si>
+  <si>
+    <t>025664</t>
+  </si>
+  <si>
+    <t>025665</t>
+  </si>
+  <si>
+    <t>025666</t>
+  </si>
+  <si>
+    <t>025667</t>
+  </si>
+  <si>
+    <t>025668</t>
+  </si>
+  <si>
+    <t>025669</t>
+  </si>
+  <si>
+    <t>025670</t>
+  </si>
+  <si>
+    <t>025671</t>
+  </si>
+  <si>
+    <t>025672</t>
+  </si>
+  <si>
+    <t>025673</t>
+  </si>
+  <si>
+    <t>025674</t>
+  </si>
+  <si>
+    <t>025675</t>
+  </si>
+  <si>
+    <t>025676</t>
+  </si>
+  <si>
+    <t>025677</t>
+  </si>
+  <si>
+    <t>025678</t>
+  </si>
+  <si>
+    <t>025679</t>
+  </si>
+  <si>
+    <t>025680</t>
+  </si>
+  <si>
+    <t>025681</t>
+  </si>
+  <si>
+    <t>025682</t>
+  </si>
+  <si>
+    <t>025683</t>
+  </si>
+  <si>
+    <t>025684</t>
+  </si>
+  <si>
+    <t>025685</t>
+  </si>
+  <si>
+    <t>025686</t>
+  </si>
+  <si>
+    <t>025687</t>
+  </si>
+  <si>
+    <t>025688</t>
+  </si>
+  <si>
+    <t>025689</t>
+  </si>
+  <si>
+    <t>025690</t>
+  </si>
+  <si>
+    <t>025691</t>
+  </si>
+  <si>
+    <t>025692</t>
+  </si>
+  <si>
+    <t>025693</t>
+  </si>
+  <si>
+    <t>025694</t>
+  </si>
+  <si>
+    <t>025695</t>
+  </si>
+  <si>
+    <t>025696</t>
+  </si>
+  <si>
+    <t>025697</t>
+  </si>
+  <si>
+    <t>025698</t>
+  </si>
+  <si>
+    <t>025699</t>
+  </si>
+  <si>
+    <t>025700</t>
+  </si>
+  <si>
+    <t>025701</t>
+  </si>
+  <si>
+    <t>025702</t>
+  </si>
+  <si>
+    <t>025703</t>
+  </si>
+  <si>
+    <t>025704</t>
+  </si>
+  <si>
+    <t>025705</t>
+  </si>
+  <si>
+    <t>025706</t>
+  </si>
+  <si>
+    <t>025707</t>
+  </si>
+  <si>
+    <t>025708</t>
+  </si>
+  <si>
+    <t>025709</t>
+  </si>
+  <si>
+    <t>025710</t>
+  </si>
+  <si>
+    <t>025711</t>
+  </si>
+  <si>
+    <t>025712</t>
+  </si>
+  <si>
+    <t>025713</t>
+  </si>
+  <si>
+    <t>025714</t>
+  </si>
+  <si>
+    <t>025715</t>
+  </si>
+  <si>
+    <t>025716</t>
+  </si>
+  <si>
+    <t>025717</t>
+  </si>
+  <si>
+    <t>025718</t>
+  </si>
+  <si>
+    <t>025719</t>
+  </si>
+  <si>
+    <t>025720</t>
+  </si>
+  <si>
+    <t>025721</t>
+  </si>
+  <si>
+    <t>025722</t>
+  </si>
+  <si>
+    <t>NOME_SITE</t>
+  </si>
+  <si>
+    <t>HOSPITAL DR ROBERTO ARNIZAUT SILVARES</t>
+  </si>
+  <si>
+    <t>HOSPITAL INFANTIL NOSSA SENHORA DA GLORIA</t>
+  </si>
+  <si>
+    <t>ES SESA GABINETE DO SECRETARIO</t>
+  </si>
+  <si>
+    <t>HOSPITAL DOUTORA RITA DE CASSIA</t>
+  </si>
+  <si>
+    <t>UNIDADE INTEGRADA JERONOMI MONTEIRO</t>
+  </si>
+  <si>
+    <t>HOSPITAL SAO JOSE</t>
+  </si>
+  <si>
+    <t>HOSPITAL DR. JOAO DOS SANTOS NEVES</t>
   </si>
 </sst>
 </file>
@@ -915,33 +1236,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7600A1C-8D91-4C3A-A5DE-920816BE31C1}">
-  <dimension ref="A1:Y100"/>
+  <dimension ref="A1:AA100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="12" customWidth="1"/>
-    <col min="10" max="10" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="37" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.140625" customWidth="1"/>
-    <col min="22" max="22" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="58" style="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -981,44 +1307,50 @@
       <c r="M1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>130</v>
       </c>
@@ -1057,29 +1389,35 @@
         <v>0</v>
       </c>
       <c r="M2" s="10"/>
-      <c r="N2" s="7" t="s">
+      <c r="N2" t="s">
+        <v>250</v>
+      </c>
+      <c r="O2" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O2" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q2" s="8">
-        <v>1</v>
-      </c>
-      <c r="R2" s="7">
+      <c r="R2" s="8">
         <v>1</v>
       </c>
       <c r="S2" s="7">
         <v>1</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="7">
+        <v>1</v>
+      </c>
+      <c r="U2" s="13" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V2" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>130</v>
       </c>
@@ -1118,29 +1456,35 @@
         <v>0</v>
       </c>
       <c r="M3" s="10"/>
-      <c r="N3" s="7" t="s">
+      <c r="N3" t="s">
+        <v>250</v>
+      </c>
+      <c r="O3" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O3" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="R3" s="8">
         <v>2</v>
       </c>
-      <c r="R3" s="7">
+      <c r="S3" s="7">
         <v>2</v>
       </c>
-      <c r="S3" s="7">
-        <v>1</v>
-      </c>
-      <c r="T3" s="13" t="s">
+      <c r="T3" s="7">
+        <v>1</v>
+      </c>
+      <c r="U3" s="13" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V3" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>130</v>
       </c>
@@ -1179,29 +1523,35 @@
         <v>0</v>
       </c>
       <c r="M4" s="10"/>
-      <c r="N4" s="7" t="s">
+      <c r="N4" t="s">
+        <v>250</v>
+      </c>
+      <c r="O4" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O4" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P4" s="8" t="s">
+      <c r="P4" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q4" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q4" s="8">
+      <c r="R4" s="8">
         <v>3</v>
       </c>
-      <c r="R4" s="7">
+      <c r="S4" s="7">
         <v>3</v>
       </c>
-      <c r="S4" s="7">
-        <v>1</v>
-      </c>
-      <c r="T4" s="13" t="s">
+      <c r="T4" s="7">
+        <v>1</v>
+      </c>
+      <c r="U4" s="13" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V4" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>130</v>
       </c>
@@ -1240,29 +1590,35 @@
         <v>0</v>
       </c>
       <c r="M5" s="10"/>
-      <c r="N5" s="7" t="s">
+      <c r="N5" t="s">
+        <v>250</v>
+      </c>
+      <c r="O5" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O5" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P5" s="8" t="s">
+      <c r="P5" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q5" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="R5" s="8">
         <v>4</v>
       </c>
-      <c r="R5" s="7">
+      <c r="S5" s="7">
         <v>4</v>
       </c>
-      <c r="S5" s="7">
-        <v>1</v>
-      </c>
-      <c r="T5" s="13" t="s">
+      <c r="T5" s="7">
+        <v>1</v>
+      </c>
+      <c r="U5" s="13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V5" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>130</v>
       </c>
@@ -1301,29 +1657,35 @@
         <v>0</v>
       </c>
       <c r="M6" s="10"/>
-      <c r="N6" s="7" t="s">
+      <c r="N6" t="s">
+        <v>250</v>
+      </c>
+      <c r="O6" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O6" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P6" s="8" t="s">
+      <c r="P6" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q6" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="R6" s="8">
         <v>5</v>
       </c>
-      <c r="R6" s="7">
+      <c r="S6" s="7">
         <v>5</v>
       </c>
-      <c r="S6" s="7">
-        <v>1</v>
-      </c>
-      <c r="T6" s="13" t="s">
+      <c r="T6" s="7">
+        <v>1</v>
+      </c>
+      <c r="U6" s="13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V6" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>130</v>
       </c>
@@ -1362,29 +1724,35 @@
         <v>0</v>
       </c>
       <c r="M7" s="10"/>
-      <c r="N7" s="7" t="s">
+      <c r="N7" t="s">
+        <v>250</v>
+      </c>
+      <c r="O7" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O7" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P7" s="8" t="s">
+      <c r="P7" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q7" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="R7" s="8">
         <v>6</v>
       </c>
-      <c r="R7" s="7">
+      <c r="S7" s="7">
         <v>6</v>
       </c>
-      <c r="S7" s="7">
-        <v>1</v>
-      </c>
-      <c r="T7" s="13" t="s">
+      <c r="T7" s="7">
+        <v>1</v>
+      </c>
+      <c r="U7" s="13" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V7" s="13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>130</v>
       </c>
@@ -1423,29 +1791,35 @@
         <v>0</v>
       </c>
       <c r="M8" s="10"/>
-      <c r="N8" s="7" t="s">
+      <c r="N8" t="s">
+        <v>250</v>
+      </c>
+      <c r="O8" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O8" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P8" s="8" t="s">
+      <c r="P8" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q8" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="R8" s="8">
         <v>7</v>
       </c>
-      <c r="R8" s="7">
+      <c r="S8" s="7">
         <v>7</v>
       </c>
-      <c r="S8" s="7">
-        <v>1</v>
-      </c>
-      <c r="T8" s="13" t="s">
+      <c r="T8" s="7">
+        <v>1</v>
+      </c>
+      <c r="U8" s="13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V8" s="13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>130</v>
       </c>
@@ -1484,29 +1858,35 @@
         <v>0</v>
       </c>
       <c r="M9" s="10"/>
-      <c r="N9" s="7" t="s">
+      <c r="N9" t="s">
+        <v>250</v>
+      </c>
+      <c r="O9" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O9" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P9" s="8" t="s">
+      <c r="P9" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q9" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="R9" s="8">
         <v>8</v>
       </c>
-      <c r="R9" s="7">
+      <c r="S9" s="7">
         <v>8</v>
       </c>
-      <c r="S9" s="7">
-        <v>1</v>
-      </c>
-      <c r="T9" s="13" t="s">
+      <c r="T9" s="7">
+        <v>1</v>
+      </c>
+      <c r="U9" s="13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V9" s="13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>130</v>
       </c>
@@ -1545,29 +1925,35 @@
         <v>0</v>
       </c>
       <c r="M10" s="10"/>
-      <c r="N10" s="7" t="s">
+      <c r="N10" t="s">
+        <v>250</v>
+      </c>
+      <c r="O10" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O10" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P10" s="8" t="s">
+      <c r="P10" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q10" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q10" s="8">
+      <c r="R10" s="8">
         <v>9</v>
       </c>
-      <c r="R10" s="7">
+      <c r="S10" s="7">
         <v>9</v>
       </c>
-      <c r="S10" s="7">
-        <v>1</v>
-      </c>
-      <c r="T10" s="13" t="s">
+      <c r="T10" s="7">
+        <v>1</v>
+      </c>
+      <c r="U10" s="13" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V10" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>130</v>
       </c>
@@ -1606,29 +1992,35 @@
         <v>0</v>
       </c>
       <c r="M11" s="10"/>
-      <c r="N11" s="7" t="s">
+      <c r="N11" t="s">
+        <v>250</v>
+      </c>
+      <c r="O11" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O11" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P11" s="8" t="s">
+      <c r="P11" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q11" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="R11" s="8">
         <v>10</v>
       </c>
-      <c r="R11" s="7">
+      <c r="S11" s="7">
         <v>10</v>
       </c>
-      <c r="S11" s="7">
-        <v>1</v>
-      </c>
-      <c r="T11" s="13" t="s">
+      <c r="T11" s="7">
+        <v>1</v>
+      </c>
+      <c r="U11" s="13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V11" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>130</v>
       </c>
@@ -1667,29 +2059,35 @@
         <v>0</v>
       </c>
       <c r="M12" s="10"/>
-      <c r="N12" s="7" t="s">
+      <c r="N12" t="s">
+        <v>250</v>
+      </c>
+      <c r="O12" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O12" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P12" s="8" t="s">
+      <c r="P12" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q12" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="R12" s="8">
         <v>11</v>
       </c>
-      <c r="R12" s="7">
+      <c r="S12" s="7">
         <v>11</v>
       </c>
-      <c r="S12" s="7">
-        <v>1</v>
-      </c>
-      <c r="T12" s="13" t="s">
+      <c r="T12" s="7">
+        <v>1</v>
+      </c>
+      <c r="U12" s="13" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V12" s="13" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>130</v>
       </c>
@@ -1728,29 +2126,35 @@
         <v>0</v>
       </c>
       <c r="M13" s="10"/>
-      <c r="N13" s="7" t="s">
+      <c r="N13" t="s">
+        <v>250</v>
+      </c>
+      <c r="O13" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O13" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P13" s="8" t="s">
+      <c r="P13" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q13" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="R13" s="8">
         <v>12</v>
       </c>
-      <c r="R13" s="7">
+      <c r="S13" s="7">
         <v>12</v>
       </c>
-      <c r="S13" s="7">
-        <v>1</v>
-      </c>
-      <c r="T13" s="13" t="s">
+      <c r="T13" s="7">
+        <v>1</v>
+      </c>
+      <c r="U13" s="13" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V13" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>130</v>
       </c>
@@ -1789,29 +2193,35 @@
         <v>0</v>
       </c>
       <c r="M14" s="10"/>
-      <c r="N14" s="7" t="s">
+      <c r="N14" t="s">
+        <v>250</v>
+      </c>
+      <c r="O14" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O14" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P14" s="8" t="s">
+      <c r="P14" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q14" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="R14" s="8">
         <v>13</v>
       </c>
-      <c r="R14" s="7">
+      <c r="S14" s="7">
         <v>13</v>
       </c>
-      <c r="S14" s="7">
-        <v>1</v>
-      </c>
-      <c r="T14" s="13" t="s">
+      <c r="T14" s="7">
+        <v>1</v>
+      </c>
+      <c r="U14" s="13" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V14" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>130</v>
       </c>
@@ -1850,29 +2260,35 @@
         <v>0</v>
       </c>
       <c r="M15" s="10"/>
-      <c r="N15" s="7" t="s">
+      <c r="N15" t="s">
+        <v>250</v>
+      </c>
+      <c r="O15" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O15" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P15" s="8" t="s">
+      <c r="P15" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q15" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="R15" s="8">
         <v>14</v>
       </c>
-      <c r="R15" s="7">
+      <c r="S15" s="7">
         <v>14</v>
       </c>
-      <c r="S15" s="7">
-        <v>1</v>
-      </c>
-      <c r="T15" s="13" t="s">
+      <c r="T15" s="7">
+        <v>1</v>
+      </c>
+      <c r="U15" s="13" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V15" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>130</v>
       </c>
@@ -1911,29 +2327,35 @@
         <v>0</v>
       </c>
       <c r="M16" s="10"/>
-      <c r="N16" s="7" t="s">
+      <c r="N16" t="s">
+        <v>250</v>
+      </c>
+      <c r="O16" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O16" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P16" s="8" t="s">
+      <c r="P16" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q16" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="R16" s="8">
         <v>15</v>
       </c>
-      <c r="R16" s="7">
+      <c r="S16" s="7">
         <v>15</v>
       </c>
-      <c r="S16" s="7">
-        <v>1</v>
-      </c>
-      <c r="T16" s="13" t="s">
+      <c r="T16" s="7">
+        <v>1</v>
+      </c>
+      <c r="U16" s="13" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V16" s="13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>130</v>
       </c>
@@ -1972,29 +2394,35 @@
         <v>0</v>
       </c>
       <c r="M17" s="10"/>
-      <c r="N17" s="7" t="s">
+      <c r="N17" t="s">
+        <v>250</v>
+      </c>
+      <c r="O17" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O17" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P17" s="8" t="s">
+      <c r="P17" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q17" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="R17" s="8">
         <v>16</v>
       </c>
-      <c r="R17" s="7">
+      <c r="S17" s="7">
         <v>16</v>
       </c>
-      <c r="S17" s="7">
-        <v>1</v>
-      </c>
-      <c r="T17" s="13" t="s">
+      <c r="T17" s="7">
+        <v>1</v>
+      </c>
+      <c r="U17" s="13" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V17" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>130</v>
       </c>
@@ -2033,29 +2461,35 @@
         <v>0</v>
       </c>
       <c r="M18" s="10"/>
-      <c r="N18" s="7" t="s">
+      <c r="N18" t="s">
+        <v>250</v>
+      </c>
+      <c r="O18" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O18" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P18" s="8" t="s">
+      <c r="P18" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q18" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q18" s="8">
+      <c r="R18" s="8">
         <v>17</v>
       </c>
-      <c r="R18" s="7">
+      <c r="S18" s="7">
         <v>17</v>
       </c>
-      <c r="S18" s="7">
-        <v>1</v>
-      </c>
-      <c r="T18" s="13" t="s">
+      <c r="T18" s="7">
+        <v>1</v>
+      </c>
+      <c r="U18" s="13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V18" s="13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>130</v>
       </c>
@@ -2094,29 +2528,35 @@
         <v>0</v>
       </c>
       <c r="M19" s="10"/>
-      <c r="N19" s="7" t="s">
+      <c r="N19" t="s">
+        <v>250</v>
+      </c>
+      <c r="O19" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O19" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P19" s="8" t="s">
+      <c r="P19" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q19" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q19" s="8">
+      <c r="R19" s="8">
         <v>18</v>
       </c>
-      <c r="R19" s="7">
+      <c r="S19" s="7">
         <v>18</v>
       </c>
-      <c r="S19" s="7">
-        <v>1</v>
-      </c>
-      <c r="T19" s="13" t="s">
+      <c r="T19" s="7">
+        <v>1</v>
+      </c>
+      <c r="U19" s="13" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V19" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>130</v>
       </c>
@@ -2155,29 +2595,35 @@
         <v>0</v>
       </c>
       <c r="M20" s="10"/>
-      <c r="N20" s="7" t="s">
+      <c r="N20" t="s">
+        <v>250</v>
+      </c>
+      <c r="O20" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O20" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P20" s="8" t="s">
+      <c r="P20" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q20" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q20" s="8">
+      <c r="R20" s="8">
         <v>19</v>
       </c>
-      <c r="R20" s="7">
+      <c r="S20" s="7">
         <v>19</v>
       </c>
-      <c r="S20" s="7">
-        <v>1</v>
-      </c>
-      <c r="T20" s="13" t="s">
+      <c r="T20" s="7">
+        <v>1</v>
+      </c>
+      <c r="U20" s="13" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V20" s="13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>130</v>
       </c>
@@ -2216,29 +2662,35 @@
         <v>0</v>
       </c>
       <c r="M21" s="10"/>
-      <c r="N21" s="7" t="s">
+      <c r="N21" t="s">
+        <v>250</v>
+      </c>
+      <c r="O21" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O21" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P21" s="8" t="s">
+      <c r="P21" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q21" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q21" s="8">
+      <c r="R21" s="8">
         <v>20</v>
       </c>
-      <c r="R21" s="7">
+      <c r="S21" s="7">
         <v>20</v>
       </c>
-      <c r="S21" s="7">
-        <v>1</v>
-      </c>
-      <c r="T21" s="13" t="s">
+      <c r="T21" s="7">
+        <v>1</v>
+      </c>
+      <c r="U21" s="13" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V21" s="13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>130</v>
       </c>
@@ -2277,29 +2729,35 @@
         <v>0</v>
       </c>
       <c r="M22" s="10"/>
-      <c r="N22" s="7" t="s">
+      <c r="N22" t="s">
+        <v>250</v>
+      </c>
+      <c r="O22" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O22" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P22" s="8" t="s">
+      <c r="P22" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q22" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q22" s="8">
+      <c r="R22" s="8">
         <v>21</v>
       </c>
-      <c r="R22" s="7">
+      <c r="S22" s="7">
         <v>21</v>
       </c>
-      <c r="S22" s="7">
-        <v>1</v>
-      </c>
-      <c r="T22" s="13" t="s">
+      <c r="T22" s="7">
+        <v>1</v>
+      </c>
+      <c r="U22" s="13" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V22" s="13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>130</v>
       </c>
@@ -2338,29 +2796,35 @@
         <v>0</v>
       </c>
       <c r="M23" s="10"/>
-      <c r="N23" s="7" t="s">
+      <c r="N23" t="s">
+        <v>250</v>
+      </c>
+      <c r="O23" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O23" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P23" s="8" t="s">
+      <c r="P23" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q23" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q23" s="8">
-        <v>22</v>
-      </c>
-      <c r="R23" s="7">
+      <c r="R23" s="8">
         <v>22</v>
       </c>
       <c r="S23" s="7">
-        <v>1</v>
-      </c>
-      <c r="T23" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="T23" s="7">
+        <v>1</v>
+      </c>
+      <c r="U23" s="13" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V23" s="13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>130</v>
       </c>
@@ -2399,29 +2863,35 @@
         <v>0</v>
       </c>
       <c r="M24" s="10"/>
-      <c r="N24" s="7" t="s">
+      <c r="N24" t="s">
+        <v>250</v>
+      </c>
+      <c r="O24" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O24" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P24" s="8" t="s">
+      <c r="P24" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q24" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q24" s="8">
+      <c r="R24" s="8">
         <v>23</v>
       </c>
-      <c r="R24" s="7">
+      <c r="S24" s="7">
         <v>23</v>
       </c>
-      <c r="S24" s="7">
-        <v>1</v>
-      </c>
-      <c r="T24" s="13" t="s">
+      <c r="T24" s="7">
+        <v>1</v>
+      </c>
+      <c r="U24" s="13" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V24" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>130</v>
       </c>
@@ -2460,29 +2930,35 @@
         <v>0</v>
       </c>
       <c r="M25" s="10"/>
-      <c r="N25" s="7" t="s">
+      <c r="N25" t="s">
+        <v>250</v>
+      </c>
+      <c r="O25" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O25" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P25" s="8" t="s">
+      <c r="P25" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q25" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q25" s="8">
+      <c r="R25" s="8">
         <v>24</v>
       </c>
-      <c r="R25" s="7">
+      <c r="S25" s="7">
         <v>24</v>
       </c>
-      <c r="S25" s="7">
-        <v>1</v>
-      </c>
-      <c r="T25" s="13" t="s">
+      <c r="T25" s="7">
+        <v>1</v>
+      </c>
+      <c r="U25" s="13" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V25" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>130</v>
       </c>
@@ -2521,29 +2997,35 @@
         <v>0</v>
       </c>
       <c r="M26" s="10"/>
-      <c r="N26" s="7" t="s">
+      <c r="N26" t="s">
+        <v>250</v>
+      </c>
+      <c r="O26" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O26" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P26" s="8" t="s">
+      <c r="P26" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q26" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q26" s="8">
+      <c r="R26" s="8">
         <v>25</v>
       </c>
-      <c r="R26" s="7">
+      <c r="S26" s="7">
         <v>25</v>
       </c>
-      <c r="S26" s="7">
-        <v>1</v>
-      </c>
-      <c r="T26" s="13" t="s">
+      <c r="T26" s="7">
+        <v>1</v>
+      </c>
+      <c r="U26" s="13" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V26" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>130</v>
       </c>
@@ -2582,29 +3064,35 @@
         <v>0</v>
       </c>
       <c r="M27" s="10"/>
-      <c r="N27" s="7" t="s">
+      <c r="N27" t="s">
+        <v>250</v>
+      </c>
+      <c r="O27" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O27" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P27" s="8" t="s">
+      <c r="P27" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q27" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q27" s="8">
+      <c r="R27" s="8">
         <v>26</v>
       </c>
-      <c r="R27" s="7">
+      <c r="S27" s="7">
         <v>26</v>
       </c>
-      <c r="S27" s="7">
-        <v>1</v>
-      </c>
-      <c r="T27" s="13" t="s">
+      <c r="T27" s="7">
+        <v>1</v>
+      </c>
+      <c r="U27" s="13" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V27" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>130</v>
       </c>
@@ -2643,29 +3131,35 @@
         <v>0</v>
       </c>
       <c r="M28" s="10"/>
-      <c r="N28" s="7" t="s">
+      <c r="N28" t="s">
+        <v>250</v>
+      </c>
+      <c r="O28" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O28" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P28" s="8" t="s">
+      <c r="P28" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q28" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q28" s="8">
+      <c r="R28" s="8">
         <v>27</v>
       </c>
-      <c r="R28" s="7">
+      <c r="S28" s="7">
         <v>27</v>
       </c>
-      <c r="S28" s="7">
-        <v>1</v>
-      </c>
-      <c r="T28" s="13" t="s">
+      <c r="T28" s="7">
+        <v>1</v>
+      </c>
+      <c r="U28" s="13" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V28" s="13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>130</v>
       </c>
@@ -2704,29 +3198,35 @@
         <v>0</v>
       </c>
       <c r="M29" s="10"/>
-      <c r="N29" s="7" t="s">
+      <c r="N29" t="s">
+        <v>250</v>
+      </c>
+      <c r="O29" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O29" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P29" s="8" t="s">
+      <c r="P29" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q29" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q29" s="8">
+      <c r="R29" s="8">
         <v>28</v>
       </c>
-      <c r="R29" s="7">
+      <c r="S29" s="7">
         <v>28</v>
       </c>
-      <c r="S29" s="7">
-        <v>1</v>
-      </c>
-      <c r="T29" s="13" t="s">
+      <c r="T29" s="7">
+        <v>1</v>
+      </c>
+      <c r="U29" s="13" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V29" s="13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>130</v>
       </c>
@@ -2765,29 +3265,35 @@
         <v>0</v>
       </c>
       <c r="M30" s="10"/>
-      <c r="N30" s="7" t="s">
+      <c r="N30" t="s">
+        <v>250</v>
+      </c>
+      <c r="O30" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O30" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P30" s="8" t="s">
+      <c r="P30" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q30" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q30" s="8">
+      <c r="R30" s="8">
         <v>29</v>
       </c>
-      <c r="R30" s="7">
+      <c r="S30" s="7">
         <v>29</v>
       </c>
-      <c r="S30" s="7">
-        <v>1</v>
-      </c>
-      <c r="T30" s="13" t="s">
+      <c r="T30" s="7">
+        <v>1</v>
+      </c>
+      <c r="U30" s="13" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V30" s="13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>130</v>
       </c>
@@ -2826,29 +3332,35 @@
         <v>0</v>
       </c>
       <c r="M31" s="10"/>
-      <c r="N31" s="7" t="s">
+      <c r="N31" t="s">
+        <v>250</v>
+      </c>
+      <c r="O31" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O31" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P31" s="8" t="s">
+      <c r="P31" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q31" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q31" s="8">
+      <c r="R31" s="8">
         <v>30</v>
       </c>
-      <c r="R31" s="7">
+      <c r="S31" s="7">
         <v>30</v>
       </c>
-      <c r="S31" s="7">
-        <v>1</v>
-      </c>
-      <c r="T31" s="13" t="s">
+      <c r="T31" s="7">
+        <v>1</v>
+      </c>
+      <c r="U31" s="13" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V31" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>130</v>
       </c>
@@ -2887,29 +3399,35 @@
         <v>0</v>
       </c>
       <c r="M32" s="10"/>
-      <c r="N32" s="7" t="s">
+      <c r="N32" t="s">
+        <v>250</v>
+      </c>
+      <c r="O32" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O32" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P32" s="8" t="s">
+      <c r="P32" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q32" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q32" s="8">
+      <c r="R32" s="8">
         <v>31</v>
       </c>
-      <c r="R32" s="7">
+      <c r="S32" s="7">
         <v>31</v>
       </c>
-      <c r="S32" s="7">
-        <v>1</v>
-      </c>
-      <c r="T32" s="13" t="s">
+      <c r="T32" s="7">
+        <v>1</v>
+      </c>
+      <c r="U32" s="13" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V32" s="13" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>130</v>
       </c>
@@ -2948,29 +3466,35 @@
         <v>0</v>
       </c>
       <c r="M33" s="10"/>
-      <c r="N33" s="7" t="s">
+      <c r="N33" t="s">
+        <v>250</v>
+      </c>
+      <c r="O33" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O33" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P33" s="8" t="s">
+      <c r="P33" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q33" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q33" s="8">
+      <c r="R33" s="8">
         <v>32</v>
       </c>
-      <c r="R33" s="7">
+      <c r="S33" s="7">
         <v>32</v>
       </c>
-      <c r="S33" s="7">
-        <v>1</v>
-      </c>
-      <c r="T33" s="13" t="s">
+      <c r="T33" s="7">
+        <v>1</v>
+      </c>
+      <c r="U33" s="13" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V33" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>130</v>
       </c>
@@ -3009,29 +3533,35 @@
         <v>0</v>
       </c>
       <c r="M34" s="10"/>
-      <c r="N34" s="7" t="s">
+      <c r="N34" t="s">
+        <v>250</v>
+      </c>
+      <c r="O34" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O34" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P34" s="8" t="s">
+      <c r="P34" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q34" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q34" s="8">
+      <c r="R34" s="8">
         <v>33</v>
       </c>
-      <c r="R34" s="7">
+      <c r="S34" s="7">
         <v>33</v>
       </c>
-      <c r="S34" s="7">
-        <v>1</v>
-      </c>
-      <c r="T34" s="13" t="s">
+      <c r="T34" s="7">
+        <v>1</v>
+      </c>
+      <c r="U34" s="13" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V34" s="13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>130</v>
       </c>
@@ -3070,29 +3600,35 @@
         <v>0</v>
       </c>
       <c r="M35" s="10"/>
-      <c r="N35" s="7" t="s">
+      <c r="N35" t="s">
+        <v>250</v>
+      </c>
+      <c r="O35" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O35" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P35" s="8" t="s">
+      <c r="P35" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q35" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q35" s="8">
+      <c r="R35" s="8">
         <v>34</v>
       </c>
-      <c r="R35" s="7">
+      <c r="S35" s="7">
         <v>34</v>
       </c>
-      <c r="S35" s="7">
-        <v>1</v>
-      </c>
-      <c r="T35" s="13" t="s">
+      <c r="T35" s="7">
+        <v>1</v>
+      </c>
+      <c r="U35" s="13" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V35" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>130</v>
       </c>
@@ -3131,29 +3667,35 @@
         <v>0</v>
       </c>
       <c r="M36" s="10"/>
-      <c r="N36" s="7" t="s">
+      <c r="N36" t="s">
+        <v>250</v>
+      </c>
+      <c r="O36" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O36" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P36" s="8" t="s">
+      <c r="P36" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q36" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q36" s="8">
+      <c r="R36" s="8">
         <v>35</v>
       </c>
-      <c r="R36" s="7">
+      <c r="S36" s="7">
         <v>35</v>
       </c>
-      <c r="S36" s="7">
-        <v>1</v>
-      </c>
-      <c r="T36" s="13" t="s">
+      <c r="T36" s="7">
+        <v>1</v>
+      </c>
+      <c r="U36" s="13" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V36" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>130</v>
       </c>
@@ -3192,29 +3734,35 @@
         <v>0</v>
       </c>
       <c r="M37" s="10"/>
-      <c r="N37" s="7" t="s">
+      <c r="N37" t="s">
+        <v>250</v>
+      </c>
+      <c r="O37" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O37" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P37" s="8" t="s">
+      <c r="P37" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q37" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q37" s="8">
+      <c r="R37" s="8">
         <v>36</v>
       </c>
-      <c r="R37" s="7">
+      <c r="S37" s="7">
         <v>36</v>
       </c>
-      <c r="S37" s="7">
-        <v>1</v>
-      </c>
-      <c r="T37" s="13" t="s">
+      <c r="T37" s="7">
+        <v>1</v>
+      </c>
+      <c r="U37" s="13" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V37" s="13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>130</v>
       </c>
@@ -3253,29 +3801,35 @@
         <v>0</v>
       </c>
       <c r="M38" s="10"/>
-      <c r="N38" s="7" t="s">
+      <c r="N38" t="s">
+        <v>250</v>
+      </c>
+      <c r="O38" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O38" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P38" s="8" t="s">
+      <c r="P38" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q38" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q38" s="8">
+      <c r="R38" s="8">
         <v>37</v>
       </c>
-      <c r="R38" s="7">
+      <c r="S38" s="7">
         <v>37</v>
       </c>
-      <c r="S38" s="7">
-        <v>1</v>
-      </c>
-      <c r="T38" s="13" t="s">
+      <c r="T38" s="7">
+        <v>1</v>
+      </c>
+      <c r="U38" s="13" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V38" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>130</v>
       </c>
@@ -3314,29 +3868,35 @@
         <v>0</v>
       </c>
       <c r="M39" s="10"/>
-      <c r="N39" s="7" t="s">
+      <c r="N39" t="s">
+        <v>250</v>
+      </c>
+      <c r="O39" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O39" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P39" s="8" t="s">
+      <c r="P39" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q39" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q39" s="8">
+      <c r="R39" s="8">
         <v>38</v>
       </c>
-      <c r="R39" s="7">
+      <c r="S39" s="7">
         <v>38</v>
       </c>
-      <c r="S39" s="7">
-        <v>1</v>
-      </c>
-      <c r="T39" s="13" t="s">
+      <c r="T39" s="7">
+        <v>1</v>
+      </c>
+      <c r="U39" s="13" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V39" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>130</v>
       </c>
@@ -3375,29 +3935,35 @@
         <v>0</v>
       </c>
       <c r="M40" s="10"/>
-      <c r="N40" s="7" t="s">
+      <c r="N40" t="s">
+        <v>250</v>
+      </c>
+      <c r="O40" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O40" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P40" s="8" t="s">
+      <c r="P40" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q40" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q40" s="8">
+      <c r="R40" s="8">
         <v>39</v>
       </c>
-      <c r="R40" s="7">
+      <c r="S40" s="7">
         <v>39</v>
       </c>
-      <c r="S40" s="7">
-        <v>1</v>
-      </c>
-      <c r="T40" s="13" t="s">
+      <c r="T40" s="7">
+        <v>1</v>
+      </c>
+      <c r="U40" s="13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V40" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>130</v>
       </c>
@@ -3436,29 +4002,35 @@
         <v>0</v>
       </c>
       <c r="M41" s="10"/>
-      <c r="N41" s="7" t="s">
+      <c r="N41" t="s">
+        <v>250</v>
+      </c>
+      <c r="O41" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O41" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P41" s="8" t="s">
+      <c r="P41" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q41" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q41" s="8">
+      <c r="R41" s="8">
         <v>40</v>
       </c>
-      <c r="R41" s="7">
+      <c r="S41" s="7">
         <v>40</v>
       </c>
-      <c r="S41" s="7">
-        <v>1</v>
-      </c>
-      <c r="T41" s="13" t="s">
+      <c r="T41" s="7">
+        <v>1</v>
+      </c>
+      <c r="U41" s="13" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V41" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>130</v>
       </c>
@@ -3497,29 +4069,35 @@
         <v>0</v>
       </c>
       <c r="M42" s="10"/>
-      <c r="N42" s="7" t="s">
+      <c r="N42" t="s">
+        <v>250</v>
+      </c>
+      <c r="O42" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O42" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P42" s="8" t="s">
+      <c r="P42" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q42" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q42" s="8">
+      <c r="R42" s="8">
         <v>41</v>
       </c>
-      <c r="R42" s="7">
+      <c r="S42" s="7">
         <v>41</v>
       </c>
-      <c r="S42" s="7">
-        <v>1</v>
-      </c>
-      <c r="T42" s="13" t="s">
+      <c r="T42" s="7">
+        <v>1</v>
+      </c>
+      <c r="U42" s="13" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V42" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>130</v>
       </c>
@@ -3558,29 +4136,35 @@
         <v>0</v>
       </c>
       <c r="M43" s="10"/>
-      <c r="N43" s="7" t="s">
+      <c r="N43" t="s">
+        <v>250</v>
+      </c>
+      <c r="O43" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O43" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P43" s="8" t="s">
+      <c r="P43" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q43" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q43" s="8">
+      <c r="R43" s="8">
         <v>42</v>
       </c>
-      <c r="R43" s="7">
+      <c r="S43" s="7">
         <v>42</v>
       </c>
-      <c r="S43" s="7">
-        <v>1</v>
-      </c>
-      <c r="T43" s="13" t="s">
+      <c r="T43" s="7">
+        <v>1</v>
+      </c>
+      <c r="U43" s="13" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V43" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>130</v>
       </c>
@@ -3619,29 +4203,35 @@
         <v>0</v>
       </c>
       <c r="M44" s="10"/>
-      <c r="N44" s="7" t="s">
+      <c r="N44" t="s">
+        <v>250</v>
+      </c>
+      <c r="O44" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O44" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P44" s="8" t="s">
+      <c r="P44" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q44" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q44" s="8">
+      <c r="R44" s="8">
         <v>43</v>
       </c>
-      <c r="R44" s="7">
+      <c r="S44" s="7">
         <v>43</v>
       </c>
-      <c r="S44" s="7">
-        <v>1</v>
-      </c>
-      <c r="T44" s="13" t="s">
+      <c r="T44" s="7">
+        <v>1</v>
+      </c>
+      <c r="U44" s="13" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V44" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>130</v>
       </c>
@@ -3680,29 +4270,35 @@
         <v>0</v>
       </c>
       <c r="M45" s="10"/>
-      <c r="N45" s="7" t="s">
+      <c r="N45" t="s">
+        <v>250</v>
+      </c>
+      <c r="O45" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O45" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P45" s="8" t="s">
+      <c r="P45" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q45" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q45" s="8">
+      <c r="R45" s="8">
         <v>44</v>
       </c>
-      <c r="R45" s="7">
+      <c r="S45" s="7">
         <v>44</v>
       </c>
-      <c r="S45" s="7">
-        <v>1</v>
-      </c>
-      <c r="T45" s="13" t="s">
+      <c r="T45" s="7">
+        <v>1</v>
+      </c>
+      <c r="U45" s="13" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V45" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>130</v>
       </c>
@@ -3741,29 +4337,35 @@
         <v>0</v>
       </c>
       <c r="M46" s="10"/>
-      <c r="N46" s="7" t="s">
+      <c r="N46" t="s">
+        <v>250</v>
+      </c>
+      <c r="O46" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O46" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P46" s="8" t="s">
+      <c r="P46" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q46" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q46" s="8">
+      <c r="R46" s="8">
         <v>45</v>
       </c>
-      <c r="R46" s="7">
+      <c r="S46" s="7">
         <v>45</v>
       </c>
-      <c r="S46" s="7">
-        <v>1</v>
-      </c>
-      <c r="T46" s="13" t="s">
+      <c r="T46" s="7">
+        <v>1</v>
+      </c>
+      <c r="U46" s="13" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V46" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>130</v>
       </c>
@@ -3802,29 +4404,35 @@
         <v>0</v>
       </c>
       <c r="M47" s="10"/>
-      <c r="N47" s="7" t="s">
+      <c r="N47" t="s">
+        <v>250</v>
+      </c>
+      <c r="O47" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O47" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P47" s="8" t="s">
+      <c r="P47" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q47" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q47" s="8">
+      <c r="R47" s="8">
         <v>46</v>
       </c>
-      <c r="R47" s="7">
+      <c r="S47" s="7">
         <v>46</v>
       </c>
-      <c r="S47" s="7">
-        <v>1</v>
-      </c>
-      <c r="T47" s="13" t="s">
+      <c r="T47" s="7">
+        <v>1</v>
+      </c>
+      <c r="U47" s="13" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V47" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>130</v>
       </c>
@@ -3863,29 +4471,35 @@
         <v>0</v>
       </c>
       <c r="M48" s="10"/>
-      <c r="N48" s="7" t="s">
+      <c r="N48" t="s">
+        <v>250</v>
+      </c>
+      <c r="O48" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O48" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P48" s="8" t="s">
+      <c r="P48" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q48" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q48" s="8">
+      <c r="R48" s="8">
         <v>47</v>
       </c>
-      <c r="R48" s="7">
+      <c r="S48" s="7">
         <v>47</v>
       </c>
-      <c r="S48" s="7">
-        <v>1</v>
-      </c>
-      <c r="T48" s="13" t="s">
+      <c r="T48" s="7">
+        <v>1</v>
+      </c>
+      <c r="U48" s="13" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V48" s="13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>130</v>
       </c>
@@ -3924,29 +4538,35 @@
         <v>0</v>
       </c>
       <c r="M49" s="10"/>
-      <c r="N49" s="7" t="s">
+      <c r="N49" t="s">
+        <v>250</v>
+      </c>
+      <c r="O49" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O49" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P49" s="8" t="s">
+      <c r="P49" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q49" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q49" s="8">
+      <c r="R49" s="8">
         <v>48</v>
       </c>
-      <c r="R49" s="7">
+      <c r="S49" s="7">
         <v>48</v>
       </c>
-      <c r="S49" s="7">
-        <v>1</v>
-      </c>
-      <c r="T49" s="13" t="s">
+      <c r="T49" s="7">
+        <v>1</v>
+      </c>
+      <c r="U49" s="13" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V49" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>130</v>
       </c>
@@ -3985,29 +4605,35 @@
         <v>0</v>
       </c>
       <c r="M50" s="10"/>
-      <c r="N50" s="7" t="s">
+      <c r="N50" t="s">
+        <v>250</v>
+      </c>
+      <c r="O50" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O50" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P50" s="8" t="s">
+      <c r="P50" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q50" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q50" s="8">
+      <c r="R50" s="8">
         <v>49</v>
       </c>
-      <c r="R50" s="7">
+      <c r="S50" s="7">
         <v>49</v>
       </c>
-      <c r="S50" s="7">
-        <v>1</v>
-      </c>
-      <c r="T50" s="13" t="s">
+      <c r="T50" s="7">
+        <v>1</v>
+      </c>
+      <c r="U50" s="13" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V50" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>130</v>
       </c>
@@ -4046,29 +4672,35 @@
         <v>0</v>
       </c>
       <c r="M51" s="10"/>
-      <c r="N51" s="7" t="s">
+      <c r="N51" t="s">
+        <v>250</v>
+      </c>
+      <c r="O51" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O51" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P51" s="8" t="s">
+      <c r="P51" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q51" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q51" s="8">
+      <c r="R51" s="8">
         <v>50</v>
       </c>
-      <c r="R51" s="7">
+      <c r="S51" s="7">
         <v>50</v>
       </c>
-      <c r="S51" s="7">
-        <v>1</v>
-      </c>
-      <c r="T51" s="13" t="s">
+      <c r="T51" s="7">
+        <v>1</v>
+      </c>
+      <c r="U51" s="13" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V51" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>141</v>
       </c>
@@ -4107,29 +4739,35 @@
         <v>0</v>
       </c>
       <c r="M52" s="10"/>
-      <c r="N52" s="7" t="s">
+      <c r="N52" t="s">
+        <v>251</v>
+      </c>
+      <c r="O52" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O52" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P52" s="8" t="s">
+      <c r="P52" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q52" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="Q52" s="8">
-        <v>1</v>
-      </c>
-      <c r="R52" s="7">
+      <c r="R52" s="8">
+        <v>1</v>
+      </c>
+      <c r="S52" s="7">
         <v>51</v>
       </c>
-      <c r="S52" s="7">
-        <v>1</v>
-      </c>
-      <c r="T52" s="13" t="s">
+      <c r="T52" s="7">
+        <v>1</v>
+      </c>
+      <c r="U52" s="13" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V52" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>141</v>
       </c>
@@ -4168,29 +4806,35 @@
         <v>0</v>
       </c>
       <c r="M53" s="10"/>
-      <c r="N53" s="7" t="s">
+      <c r="N53" t="s">
+        <v>251</v>
+      </c>
+      <c r="O53" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O53" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P53" s="8" t="s">
+      <c r="P53" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q53" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="Q53" s="8">
+      <c r="R53" s="8">
         <v>2</v>
       </c>
-      <c r="R53" s="7">
+      <c r="S53" s="7">
         <v>52</v>
       </c>
-      <c r="S53" s="7">
-        <v>1</v>
-      </c>
-      <c r="T53" s="13" t="s">
+      <c r="T53" s="7">
+        <v>1</v>
+      </c>
+      <c r="U53" s="13" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V53" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>141</v>
       </c>
@@ -4229,29 +4873,35 @@
         <v>0</v>
       </c>
       <c r="M54" s="10"/>
-      <c r="N54" s="7" t="s">
+      <c r="N54" t="s">
+        <v>251</v>
+      </c>
+      <c r="O54" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O54" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P54" s="8" t="s">
+      <c r="P54" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q54" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="Q54" s="8">
+      <c r="R54" s="8">
         <v>3</v>
       </c>
-      <c r="R54" s="7">
+      <c r="S54" s="7">
         <v>53</v>
       </c>
-      <c r="S54" s="7">
-        <v>1</v>
-      </c>
-      <c r="T54" s="13" t="s">
+      <c r="T54" s="7">
+        <v>1</v>
+      </c>
+      <c r="U54" s="13" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V54" s="13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>141</v>
       </c>
@@ -4290,29 +4940,35 @@
         <v>0</v>
       </c>
       <c r="M55" s="10"/>
-      <c r="N55" s="7" t="s">
+      <c r="N55" t="s">
+        <v>251</v>
+      </c>
+      <c r="O55" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O55" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P55" s="8" t="s">
+      <c r="P55" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q55" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="Q55" s="8">
+      <c r="R55" s="8">
         <v>4</v>
       </c>
-      <c r="R55" s="7">
+      <c r="S55" s="7">
         <v>54</v>
       </c>
-      <c r="S55" s="7">
-        <v>1</v>
-      </c>
-      <c r="T55" s="13" t="s">
+      <c r="T55" s="7">
+        <v>1</v>
+      </c>
+      <c r="U55" s="13" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V55" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>141</v>
       </c>
@@ -4351,29 +5007,35 @@
         <v>0</v>
       </c>
       <c r="M56" s="10"/>
-      <c r="N56" s="7" t="s">
+      <c r="N56" t="s">
+        <v>251</v>
+      </c>
+      <c r="O56" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O56" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P56" s="8" t="s">
+      <c r="P56" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q56" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="Q56" s="8">
+      <c r="R56" s="8">
         <v>5</v>
       </c>
-      <c r="R56" s="7">
+      <c r="S56" s="7">
         <v>55</v>
       </c>
-      <c r="S56" s="7">
-        <v>1</v>
-      </c>
-      <c r="T56" s="13" t="s">
+      <c r="T56" s="7">
+        <v>1</v>
+      </c>
+      <c r="U56" s="13" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V56" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>141</v>
       </c>
@@ -4412,29 +5074,35 @@
         <v>0</v>
       </c>
       <c r="M57" s="10"/>
-      <c r="N57" s="7" t="s">
+      <c r="N57" t="s">
+        <v>251</v>
+      </c>
+      <c r="O57" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O57" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P57" s="8" t="s">
+      <c r="P57" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q57" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="Q57" s="8">
+      <c r="R57" s="8">
         <v>6</v>
       </c>
-      <c r="R57" s="7">
+      <c r="S57" s="7">
         <v>56</v>
       </c>
-      <c r="S57" s="7">
-        <v>1</v>
-      </c>
-      <c r="T57" s="13" t="s">
+      <c r="T57" s="7">
+        <v>1</v>
+      </c>
+      <c r="U57" s="13" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V57" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>141</v>
       </c>
@@ -4473,29 +5141,35 @@
         <v>0</v>
       </c>
       <c r="M58" s="10"/>
-      <c r="N58" s="7" t="s">
+      <c r="N58" t="s">
+        <v>251</v>
+      </c>
+      <c r="O58" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O58" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P58" s="8" t="s">
+      <c r="P58" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q58" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="Q58" s="8">
+      <c r="R58" s="8">
         <v>7</v>
       </c>
-      <c r="R58" s="7">
+      <c r="S58" s="7">
         <v>57</v>
       </c>
-      <c r="S58" s="7">
-        <v>1</v>
-      </c>
-      <c r="T58" s="13" t="s">
+      <c r="T58" s="7">
+        <v>1</v>
+      </c>
+      <c r="U58" s="13" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V58" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>141</v>
       </c>
@@ -4534,29 +5208,35 @@
         <v>0</v>
       </c>
       <c r="M59" s="10"/>
-      <c r="N59" s="7" t="s">
+      <c r="N59" t="s">
+        <v>251</v>
+      </c>
+      <c r="O59" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O59" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P59" s="8" t="s">
+      <c r="P59" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q59" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="Q59" s="8">
+      <c r="R59" s="8">
         <v>8</v>
       </c>
-      <c r="R59" s="7">
+      <c r="S59" s="7">
         <v>58</v>
       </c>
-      <c r="S59" s="7">
-        <v>1</v>
-      </c>
-      <c r="T59" s="13" t="s">
+      <c r="T59" s="7">
+        <v>1</v>
+      </c>
+      <c r="U59" s="13" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V59" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>141</v>
       </c>
@@ -4595,29 +5275,35 @@
         <v>0</v>
       </c>
       <c r="M60" s="10"/>
-      <c r="N60" s="7" t="s">
+      <c r="N60" t="s">
+        <v>251</v>
+      </c>
+      <c r="O60" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O60" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P60" s="8" t="s">
+      <c r="P60" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q60" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="Q60" s="8">
+      <c r="R60" s="8">
         <v>9</v>
       </c>
-      <c r="R60" s="7">
+      <c r="S60" s="7">
         <v>59</v>
       </c>
-      <c r="S60" s="7">
-        <v>1</v>
-      </c>
-      <c r="T60" s="13" t="s">
+      <c r="T60" s="7">
+        <v>1</v>
+      </c>
+      <c r="U60" s="13" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V60" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>141</v>
       </c>
@@ -4656,29 +5342,35 @@
         <v>0</v>
       </c>
       <c r="M61" s="10"/>
-      <c r="N61" s="7" t="s">
+      <c r="N61" t="s">
+        <v>251</v>
+      </c>
+      <c r="O61" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O61" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P61" s="8" t="s">
+      <c r="P61" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q61" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="Q61" s="8">
+      <c r="R61" s="8">
         <v>10</v>
       </c>
-      <c r="R61" s="7">
+      <c r="S61" s="7">
         <v>60</v>
       </c>
-      <c r="S61" s="7">
-        <v>1</v>
-      </c>
-      <c r="T61" s="13" t="s">
+      <c r="T61" s="7">
+        <v>1</v>
+      </c>
+      <c r="U61" s="13" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V61" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>141</v>
       </c>
@@ -4717,29 +5409,35 @@
         <v>0</v>
       </c>
       <c r="M62" s="10"/>
-      <c r="N62" s="7" t="s">
+      <c r="N62" t="s">
+        <v>254</v>
+      </c>
+      <c r="O62" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O62" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P62" s="8" t="s">
+      <c r="P62" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q62" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q62" s="8">
-        <v>1</v>
-      </c>
-      <c r="R62" s="7">
+      <c r="R62" s="8">
+        <v>1</v>
+      </c>
+      <c r="S62" s="7">
         <v>61</v>
       </c>
-      <c r="S62" s="7">
-        <v>1</v>
-      </c>
-      <c r="T62" s="13" t="s">
+      <c r="T62" s="7">
+        <v>1</v>
+      </c>
+      <c r="U62" s="13" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V62" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>141</v>
       </c>
@@ -4778,29 +5476,35 @@
         <v>0</v>
       </c>
       <c r="M63" s="10"/>
-      <c r="N63" s="7" t="s">
+      <c r="N63" t="s">
+        <v>254</v>
+      </c>
+      <c r="O63" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O63" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P63" s="8" t="s">
+      <c r="P63" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q63" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q63" s="8">
+      <c r="R63" s="8">
         <v>2</v>
       </c>
-      <c r="R63" s="7">
+      <c r="S63" s="7">
         <v>62</v>
       </c>
-      <c r="S63" s="7">
-        <v>1</v>
-      </c>
-      <c r="T63" s="13" t="s">
+      <c r="T63" s="7">
+        <v>1</v>
+      </c>
+      <c r="U63" s="13" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V63" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>141</v>
       </c>
@@ -4839,29 +5543,35 @@
         <v>0</v>
       </c>
       <c r="M64" s="10"/>
-      <c r="N64" s="7" t="s">
+      <c r="N64" t="s">
+        <v>254</v>
+      </c>
+      <c r="O64" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O64" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P64" s="8" t="s">
+      <c r="P64" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q64" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q64" s="8">
+      <c r="R64" s="8">
         <v>3</v>
       </c>
-      <c r="R64" s="7">
+      <c r="S64" s="7">
         <v>63</v>
       </c>
-      <c r="S64" s="7">
-        <v>1</v>
-      </c>
-      <c r="T64" s="13" t="s">
+      <c r="T64" s="7">
+        <v>1</v>
+      </c>
+      <c r="U64" s="13" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V64" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>141</v>
       </c>
@@ -4900,29 +5610,35 @@
         <v>0</v>
       </c>
       <c r="M65" s="10"/>
-      <c r="N65" s="7" t="s">
+      <c r="N65" t="s">
+        <v>254</v>
+      </c>
+      <c r="O65" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O65" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P65" s="8" t="s">
+      <c r="P65" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q65" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q65" s="8">
+      <c r="R65" s="8">
         <v>4</v>
       </c>
-      <c r="R65" s="7">
+      <c r="S65" s="7">
         <v>64</v>
       </c>
-      <c r="S65" s="7">
-        <v>1</v>
-      </c>
-      <c r="T65" s="13" t="s">
+      <c r="T65" s="7">
+        <v>1</v>
+      </c>
+      <c r="U65" s="13" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V65" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>141</v>
       </c>
@@ -4961,29 +5677,35 @@
         <v>0</v>
       </c>
       <c r="M66" s="10"/>
-      <c r="N66" s="7" t="s">
+      <c r="N66" t="s">
+        <v>254</v>
+      </c>
+      <c r="O66" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O66" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P66" s="8" t="s">
+      <c r="P66" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q66" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q66" s="8">
+      <c r="R66" s="8">
         <v>5</v>
       </c>
-      <c r="R66" s="7">
+      <c r="S66" s="7">
         <v>65</v>
       </c>
-      <c r="S66" s="7">
-        <v>1</v>
-      </c>
-      <c r="T66" s="13" t="s">
+      <c r="T66" s="7">
+        <v>1</v>
+      </c>
+      <c r="U66" s="13" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V66" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>141</v>
       </c>
@@ -5022,29 +5744,35 @@
         <v>0</v>
       </c>
       <c r="M67" s="10"/>
-      <c r="N67" s="7" t="s">
+      <c r="N67" t="s">
+        <v>254</v>
+      </c>
+      <c r="O67" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O67" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P67" s="8" t="s">
+      <c r="P67" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q67" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q67" s="8">
+      <c r="R67" s="8">
         <v>6</v>
       </c>
-      <c r="R67" s="7">
+      <c r="S67" s="7">
         <v>66</v>
       </c>
-      <c r="S67" s="7">
-        <v>1</v>
-      </c>
-      <c r="T67" s="13" t="s">
+      <c r="T67" s="7">
+        <v>1</v>
+      </c>
+      <c r="U67" s="13" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V67" s="13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>141</v>
       </c>
@@ -5083,29 +5811,35 @@
         <v>0</v>
       </c>
       <c r="M68" s="10"/>
-      <c r="N68" s="7" t="s">
+      <c r="N68" t="s">
+        <v>254</v>
+      </c>
+      <c r="O68" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O68" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P68" s="8" t="s">
+      <c r="P68" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q68" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q68" s="8">
+      <c r="R68" s="8">
         <v>7</v>
       </c>
-      <c r="R68" s="7">
+      <c r="S68" s="7">
         <v>67</v>
       </c>
-      <c r="S68" s="7">
-        <v>1</v>
-      </c>
-      <c r="T68" s="13" t="s">
+      <c r="T68" s="7">
+        <v>1</v>
+      </c>
+      <c r="U68" s="13" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V68" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>141</v>
       </c>
@@ -5144,29 +5878,35 @@
         <v>0</v>
       </c>
       <c r="M69" s="10"/>
-      <c r="N69" s="7" t="s">
+      <c r="N69" t="s">
+        <v>254</v>
+      </c>
+      <c r="O69" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O69" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P69" s="8" t="s">
+      <c r="P69" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q69" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q69" s="8">
+      <c r="R69" s="8">
         <v>8</v>
       </c>
-      <c r="R69" s="7">
+      <c r="S69" s="7">
         <v>68</v>
       </c>
-      <c r="S69" s="7">
-        <v>1</v>
-      </c>
-      <c r="T69" s="13" t="s">
+      <c r="T69" s="7">
+        <v>1</v>
+      </c>
+      <c r="U69" s="13" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V69" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>141</v>
       </c>
@@ -5205,29 +5945,35 @@
         <v>0</v>
       </c>
       <c r="M70" s="10"/>
-      <c r="N70" s="7" t="s">
+      <c r="N70" t="s">
+        <v>254</v>
+      </c>
+      <c r="O70" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O70" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P70" s="8" t="s">
+      <c r="P70" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q70" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q70" s="8">
+      <c r="R70" s="8">
         <v>9</v>
       </c>
-      <c r="R70" s="7">
+      <c r="S70" s="7">
         <v>69</v>
       </c>
-      <c r="S70" s="7">
-        <v>1</v>
-      </c>
-      <c r="T70" s="13" t="s">
+      <c r="T70" s="7">
+        <v>1</v>
+      </c>
+      <c r="U70" s="13" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V70" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>141</v>
       </c>
@@ -5266,29 +6012,35 @@
         <v>0</v>
       </c>
       <c r="M71" s="10"/>
-      <c r="N71" s="7" t="s">
+      <c r="N71" t="s">
+        <v>254</v>
+      </c>
+      <c r="O71" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O71" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P71" s="8" t="s">
+      <c r="P71" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q71" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q71" s="8">
+      <c r="R71" s="8">
         <v>10</v>
       </c>
-      <c r="R71" s="7">
+      <c r="S71" s="7">
         <v>70</v>
       </c>
-      <c r="S71" s="7">
-        <v>1</v>
-      </c>
-      <c r="T71" s="13" t="s">
+      <c r="T71" s="7">
+        <v>1</v>
+      </c>
+      <c r="U71" s="13" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V71" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
         <v>141</v>
       </c>
@@ -5327,29 +6079,35 @@
         <v>0</v>
       </c>
       <c r="M72" s="10"/>
-      <c r="N72" s="7" t="s">
+      <c r="N72" t="s">
+        <v>253</v>
+      </c>
+      <c r="O72" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O72" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P72" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q72" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q72" s="8">
-        <v>1</v>
-      </c>
-      <c r="R72" s="7">
+      <c r="R72" s="8">
+        <v>1</v>
+      </c>
+      <c r="S72" s="7">
         <v>71</v>
       </c>
-      <c r="S72" s="7">
-        <v>1</v>
-      </c>
-      <c r="T72" s="13" t="s">
+      <c r="T72" s="7">
+        <v>1</v>
+      </c>
+      <c r="U72" s="13" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V72" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
         <v>141</v>
       </c>
@@ -5388,29 +6146,35 @@
         <v>0</v>
       </c>
       <c r="M73" s="10"/>
-      <c r="N73" s="7" t="s">
+      <c r="N73" t="s">
+        <v>253</v>
+      </c>
+      <c r="O73" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O73" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P73" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q73" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q73" s="8">
+      <c r="R73" s="8">
         <v>2</v>
       </c>
-      <c r="R73" s="7">
+      <c r="S73" s="7">
         <v>72</v>
       </c>
-      <c r="S73" s="7">
-        <v>1</v>
-      </c>
-      <c r="T73" s="13" t="s">
+      <c r="T73" s="7">
+        <v>1</v>
+      </c>
+      <c r="U73" s="13" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V73" s="13" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
         <v>141</v>
       </c>
@@ -5449,29 +6213,35 @@
         <v>0</v>
       </c>
       <c r="M74" s="10"/>
-      <c r="N74" s="7" t="s">
+      <c r="N74" t="s">
+        <v>253</v>
+      </c>
+      <c r="O74" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O74" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P74" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q74" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q74" s="8">
+      <c r="R74" s="8">
         <v>3</v>
       </c>
-      <c r="R74" s="7">
+      <c r="S74" s="7">
         <v>73</v>
       </c>
-      <c r="S74" s="7">
-        <v>1</v>
-      </c>
-      <c r="T74" s="13" t="s">
+      <c r="T74" s="7">
+        <v>1</v>
+      </c>
+      <c r="U74" s="13" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V74" s="13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
         <v>141</v>
       </c>
@@ -5510,29 +6280,35 @@
         <v>0</v>
       </c>
       <c r="M75" s="10"/>
-      <c r="N75" s="7" t="s">
+      <c r="N75" t="s">
+        <v>253</v>
+      </c>
+      <c r="O75" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O75" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P75" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q75" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q75" s="8">
+      <c r="R75" s="8">
         <v>4</v>
       </c>
-      <c r="R75" s="7">
+      <c r="S75" s="7">
         <v>74</v>
       </c>
-      <c r="S75" s="7">
-        <v>1</v>
-      </c>
-      <c r="T75" s="13" t="s">
+      <c r="T75" s="7">
+        <v>1</v>
+      </c>
+      <c r="U75" s="13" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V75" s="13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
         <v>141</v>
       </c>
@@ -5571,29 +6347,35 @@
         <v>0</v>
       </c>
       <c r="M76" s="10"/>
-      <c r="N76" s="7" t="s">
+      <c r="N76" t="s">
+        <v>253</v>
+      </c>
+      <c r="O76" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O76" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P76" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q76" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q76" s="8">
+      <c r="R76" s="8">
         <v>5</v>
       </c>
-      <c r="R76" s="7">
+      <c r="S76" s="7">
         <v>75</v>
       </c>
-      <c r="S76" s="7">
-        <v>1</v>
-      </c>
-      <c r="T76" s="13" t="s">
+      <c r="T76" s="7">
+        <v>1</v>
+      </c>
+      <c r="U76" s="13" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V76" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
         <v>141</v>
       </c>
@@ -5632,29 +6414,35 @@
         <v>0</v>
       </c>
       <c r="M77" s="10"/>
-      <c r="N77" s="7" t="s">
+      <c r="N77" t="s">
+        <v>253</v>
+      </c>
+      <c r="O77" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O77" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P77" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q77" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q77" s="8">
+      <c r="R77" s="8">
         <v>6</v>
       </c>
-      <c r="R77" s="7">
+      <c r="S77" s="7">
         <v>76</v>
       </c>
-      <c r="S77" s="7">
-        <v>1</v>
-      </c>
-      <c r="T77" s="13" t="s">
+      <c r="T77" s="7">
+        <v>1</v>
+      </c>
+      <c r="U77" s="13" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V77" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
         <v>141</v>
       </c>
@@ -5693,29 +6481,35 @@
         <v>0</v>
       </c>
       <c r="M78" s="10"/>
-      <c r="N78" s="7" t="s">
+      <c r="N78" t="s">
+        <v>253</v>
+      </c>
+      <c r="O78" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O78" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P78" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q78" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q78" s="8">
+      <c r="R78" s="8">
         <v>7</v>
       </c>
-      <c r="R78" s="7">
+      <c r="S78" s="7">
         <v>77</v>
       </c>
-      <c r="S78" s="7">
-        <v>1</v>
-      </c>
-      <c r="T78" s="13" t="s">
+      <c r="T78" s="7">
+        <v>1</v>
+      </c>
+      <c r="U78" s="13" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V78" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>141</v>
       </c>
@@ -5754,29 +6548,35 @@
         <v>0</v>
       </c>
       <c r="M79" s="10"/>
-      <c r="N79" s="7" t="s">
+      <c r="N79" t="s">
+        <v>253</v>
+      </c>
+      <c r="O79" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O79" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P79" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q79" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q79" s="8">
+      <c r="R79" s="8">
         <v>8</v>
       </c>
-      <c r="R79" s="7">
+      <c r="S79" s="7">
         <v>78</v>
       </c>
-      <c r="S79" s="7">
-        <v>1</v>
-      </c>
-      <c r="T79" s="13" t="s">
+      <c r="T79" s="7">
+        <v>1</v>
+      </c>
+      <c r="U79" s="13" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V79" s="13" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
         <v>141</v>
       </c>
@@ -5815,29 +6615,35 @@
         <v>0</v>
       </c>
       <c r="M80" s="10"/>
-      <c r="N80" s="7" t="s">
+      <c r="N80" t="s">
+        <v>253</v>
+      </c>
+      <c r="O80" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O80" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P80" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q80" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q80" s="8">
+      <c r="R80" s="8">
         <v>9</v>
       </c>
-      <c r="R80" s="7">
+      <c r="S80" s="7">
         <v>79</v>
       </c>
-      <c r="S80" s="7">
-        <v>1</v>
-      </c>
-      <c r="T80" s="13" t="s">
+      <c r="T80" s="7">
+        <v>1</v>
+      </c>
+      <c r="U80" s="13" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V80" s="13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
         <v>141</v>
       </c>
@@ -5876,29 +6682,35 @@
         <v>0</v>
       </c>
       <c r="M81" s="10"/>
-      <c r="N81" s="7" t="s">
+      <c r="N81" t="s">
+        <v>253</v>
+      </c>
+      <c r="O81" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O81" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P81" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q81" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q81" s="8">
+      <c r="R81" s="8">
         <v>10</v>
       </c>
-      <c r="R81" s="7">
+      <c r="S81" s="7">
         <v>80</v>
       </c>
-      <c r="S81" s="7">
-        <v>1</v>
-      </c>
-      <c r="T81" s="13" t="s">
+      <c r="T81" s="7">
+        <v>1</v>
+      </c>
+      <c r="U81" s="13" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V81" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>142</v>
       </c>
@@ -5937,29 +6749,35 @@
         <v>0</v>
       </c>
       <c r="M82" s="10"/>
-      <c r="N82" s="7" t="s">
+      <c r="N82" t="s">
+        <v>249</v>
+      </c>
+      <c r="O82" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O82" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P82" s="11" t="s">
+      <c r="P82" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q82" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="Q82" s="8">
-        <v>1</v>
-      </c>
-      <c r="R82" s="7">
+      <c r="R82" s="8">
+        <v>1</v>
+      </c>
+      <c r="S82" s="7">
         <v>81</v>
       </c>
-      <c r="S82" s="7">
-        <v>1</v>
-      </c>
-      <c r="T82" s="13" t="s">
+      <c r="T82" s="7">
+        <v>1</v>
+      </c>
+      <c r="U82" s="13" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V82" s="13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
         <v>142</v>
       </c>
@@ -5998,29 +6816,35 @@
         <v>0</v>
       </c>
       <c r="M83" s="10"/>
-      <c r="N83" s="7" t="s">
+      <c r="N83" t="s">
+        <v>249</v>
+      </c>
+      <c r="O83" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O83" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P83" s="11" t="s">
+      <c r="P83" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q83" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="Q83" s="8">
+      <c r="R83" s="8">
         <v>2</v>
       </c>
-      <c r="R83" s="7">
+      <c r="S83" s="7">
         <v>82</v>
       </c>
-      <c r="S83" s="7">
-        <v>1</v>
-      </c>
-      <c r="T83" s="13" t="s">
+      <c r="T83" s="7">
+        <v>1</v>
+      </c>
+      <c r="U83" s="13" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V83" s="13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>142</v>
       </c>
@@ -6059,29 +6883,35 @@
         <v>0</v>
       </c>
       <c r="M84" s="10"/>
-      <c r="N84" s="7" t="s">
+      <c r="N84" t="s">
+        <v>249</v>
+      </c>
+      <c r="O84" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O84" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P84" s="11" t="s">
+      <c r="P84" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q84" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="Q84" s="8">
+      <c r="R84" s="8">
         <v>3</v>
       </c>
-      <c r="R84" s="7">
+      <c r="S84" s="7">
         <v>83</v>
       </c>
-      <c r="S84" s="7">
-        <v>1</v>
-      </c>
-      <c r="T84" s="13" t="s">
+      <c r="T84" s="7">
+        <v>1</v>
+      </c>
+      <c r="U84" s="13" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V84" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
         <v>142</v>
       </c>
@@ -6120,29 +6950,35 @@
         <v>0</v>
       </c>
       <c r="M85" s="10"/>
-      <c r="N85" s="7" t="s">
+      <c r="N85" t="s">
+        <v>249</v>
+      </c>
+      <c r="O85" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O85" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P85" s="11" t="s">
+      <c r="P85" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q85" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="Q85" s="8">
+      <c r="R85" s="8">
         <v>4</v>
       </c>
-      <c r="R85" s="7">
+      <c r="S85" s="7">
         <v>84</v>
       </c>
-      <c r="S85" s="7">
-        <v>1</v>
-      </c>
-      <c r="T85" s="13" t="s">
+      <c r="T85" s="7">
+        <v>1</v>
+      </c>
+      <c r="U85" s="13" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V85" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
         <v>142</v>
       </c>
@@ -6181,29 +7017,35 @@
         <v>0</v>
       </c>
       <c r="M86" s="10"/>
-      <c r="N86" s="7" t="s">
+      <c r="N86" t="s">
+        <v>249</v>
+      </c>
+      <c r="O86" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O86" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P86" s="11" t="s">
+      <c r="P86" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q86" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="Q86" s="8">
+      <c r="R86" s="8">
         <v>5</v>
       </c>
-      <c r="R86" s="7">
+      <c r="S86" s="7">
         <v>85</v>
       </c>
-      <c r="S86" s="7">
-        <v>1</v>
-      </c>
-      <c r="T86" s="13" t="s">
+      <c r="T86" s="7">
+        <v>1</v>
+      </c>
+      <c r="U86" s="13" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V86" s="13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
         <v>143</v>
       </c>
@@ -6242,29 +7084,35 @@
         <v>0</v>
       </c>
       <c r="M87" s="10"/>
-      <c r="N87" s="7" t="s">
+      <c r="N87" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="O87" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O87" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P87" s="11" t="s">
+      <c r="P87" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q87" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="Q87" s="8">
-        <v>1</v>
-      </c>
-      <c r="R87" s="7">
+      <c r="R87" s="8">
+        <v>1</v>
+      </c>
+      <c r="S87" s="7">
         <v>86</v>
       </c>
-      <c r="S87" s="7">
-        <v>1</v>
-      </c>
-      <c r="T87" s="13" t="s">
+      <c r="T87" s="7">
+        <v>1</v>
+      </c>
+      <c r="U87" s="13" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V87" s="13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>143</v>
       </c>
@@ -6303,29 +7151,35 @@
         <v>0</v>
       </c>
       <c r="M88" s="10"/>
-      <c r="N88" s="7" t="s">
+      <c r="N88" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="O88" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O88" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P88" s="11" t="s">
+      <c r="P88" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q88" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="Q88" s="8">
+      <c r="R88" s="8">
         <v>2</v>
       </c>
-      <c r="R88" s="7">
+      <c r="S88" s="7">
         <v>87</v>
       </c>
-      <c r="S88" s="7">
-        <v>1</v>
-      </c>
-      <c r="T88" s="13" t="s">
+      <c r="T88" s="7">
+        <v>1</v>
+      </c>
+      <c r="U88" s="13" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V88" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
         <v>141</v>
       </c>
@@ -6364,29 +7218,35 @@
         <v>0</v>
       </c>
       <c r="M89" s="10"/>
-      <c r="N89" s="7" t="s">
+      <c r="N89" t="s">
+        <v>252</v>
+      </c>
+      <c r="O89" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="O89" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P89" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q89" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="Q89" s="8">
-        <v>1</v>
-      </c>
-      <c r="R89" s="7">
+      <c r="R89" s="8">
+        <v>1</v>
+      </c>
+      <c r="S89" s="7">
         <v>88</v>
       </c>
-      <c r="S89" s="7">
-        <v>1</v>
-      </c>
-      <c r="T89" s="13" t="s">
+      <c r="T89" s="7">
+        <v>1</v>
+      </c>
+      <c r="U89" s="13" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V89" s="13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
         <v>141</v>
       </c>
@@ -6425,29 +7285,35 @@
         <v>0</v>
       </c>
       <c r="M90" s="10"/>
-      <c r="N90" s="7" t="s">
+      <c r="N90" t="s">
+        <v>252</v>
+      </c>
+      <c r="O90" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="O90" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P90" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q90" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="Q90" s="8">
+      <c r="R90" s="8">
         <v>2</v>
       </c>
-      <c r="R90" s="7">
+      <c r="S90" s="7">
         <v>89</v>
       </c>
-      <c r="S90" s="7">
-        <v>1</v>
-      </c>
-      <c r="T90" s="13" t="s">
+      <c r="T90" s="7">
+        <v>1</v>
+      </c>
+      <c r="U90" s="13" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V90" s="13" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
         <v>141</v>
       </c>
@@ -6486,29 +7352,35 @@
         <v>0</v>
       </c>
       <c r="M91" s="10"/>
-      <c r="N91" s="7" t="s">
+      <c r="N91" t="s">
+        <v>252</v>
+      </c>
+      <c r="O91" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="O91" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P91" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q91" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="Q91" s="8">
+      <c r="R91" s="8">
         <v>3</v>
       </c>
-      <c r="R91" s="7">
+      <c r="S91" s="7">
         <v>90</v>
       </c>
-      <c r="S91" s="7">
-        <v>1</v>
-      </c>
-      <c r="T91" s="13" t="s">
+      <c r="T91" s="7">
+        <v>1</v>
+      </c>
+      <c r="U91" s="13" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V91" s="13" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>141</v>
       </c>
@@ -6547,29 +7419,35 @@
         <v>0</v>
       </c>
       <c r="M92" s="10"/>
-      <c r="N92" s="7" t="s">
+      <c r="N92" t="s">
+        <v>252</v>
+      </c>
+      <c r="O92" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="O92" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P92" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q92" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="Q92" s="8">
+      <c r="R92" s="8">
         <v>4</v>
       </c>
-      <c r="R92" s="7">
+      <c r="S92" s="7">
         <v>91</v>
       </c>
-      <c r="S92" s="7">
-        <v>1</v>
-      </c>
-      <c r="T92" s="13" t="s">
+      <c r="T92" s="7">
+        <v>1</v>
+      </c>
+      <c r="U92" s="13" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V92" s="13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
         <v>141</v>
       </c>
@@ -6608,29 +7486,35 @@
         <v>0</v>
       </c>
       <c r="M93" s="10"/>
-      <c r="N93" s="7" t="s">
+      <c r="N93" t="s">
+        <v>252</v>
+      </c>
+      <c r="O93" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="O93" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P93" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q93" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="Q93" s="8">
+      <c r="R93" s="8">
         <v>5</v>
       </c>
-      <c r="R93" s="7">
+      <c r="S93" s="7">
         <v>92</v>
       </c>
-      <c r="S93" s="7">
-        <v>1</v>
-      </c>
-      <c r="T93" s="13" t="s">
+      <c r="T93" s="7">
+        <v>1</v>
+      </c>
+      <c r="U93" s="13" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V93" s="13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
         <v>141</v>
       </c>
@@ -6669,29 +7553,35 @@
         <v>0</v>
       </c>
       <c r="M94" s="10"/>
-      <c r="N94" s="7" t="s">
+      <c r="N94" t="s">
+        <v>252</v>
+      </c>
+      <c r="O94" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="O94" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P94" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q94" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="Q94" s="8">
+      <c r="R94" s="8">
         <v>6</v>
       </c>
-      <c r="R94" s="7">
+      <c r="S94" s="7">
         <v>93</v>
       </c>
-      <c r="S94" s="7">
-        <v>1</v>
-      </c>
-      <c r="T94" s="13" t="s">
+      <c r="T94" s="7">
+        <v>1</v>
+      </c>
+      <c r="U94" s="13" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V94" s="13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
         <v>141</v>
       </c>
@@ -6730,29 +7620,35 @@
         <v>0</v>
       </c>
       <c r="M95" s="10"/>
-      <c r="N95" s="7" t="s">
+      <c r="N95" t="s">
+        <v>252</v>
+      </c>
+      <c r="O95" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="O95" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P95" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q95" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="Q95" s="8">
+      <c r="R95" s="8">
         <v>7</v>
       </c>
-      <c r="R95" s="7">
+      <c r="S95" s="7">
         <v>94</v>
       </c>
-      <c r="S95" s="7">
-        <v>1</v>
-      </c>
-      <c r="T95" s="13" t="s">
+      <c r="T95" s="7">
+        <v>1</v>
+      </c>
+      <c r="U95" s="13" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V95" s="13" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
         <v>141</v>
       </c>
@@ -6791,29 +7687,35 @@
         <v>0</v>
       </c>
       <c r="M96" s="10"/>
-      <c r="N96" s="7" t="s">
+      <c r="N96" t="s">
+        <v>252</v>
+      </c>
+      <c r="O96" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="O96" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P96" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q96" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="Q96" s="8">
+      <c r="R96" s="8">
         <v>8</v>
       </c>
-      <c r="R96" s="7">
+      <c r="S96" s="7">
         <v>95</v>
       </c>
-      <c r="S96" s="7">
-        <v>1</v>
-      </c>
-      <c r="T96" s="13" t="s">
+      <c r="T96" s="7">
+        <v>1</v>
+      </c>
+      <c r="U96" s="13" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V96" s="13" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
         <v>141</v>
       </c>
@@ -6852,29 +7754,35 @@
         <v>0</v>
       </c>
       <c r="M97" s="10"/>
-      <c r="N97" s="7" t="s">
+      <c r="N97" t="s">
+        <v>252</v>
+      </c>
+      <c r="O97" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="O97" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P97" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q97" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="Q97" s="8">
+      <c r="R97" s="8">
         <v>9</v>
       </c>
-      <c r="R97" s="7">
+      <c r="S97" s="7">
         <v>96</v>
       </c>
-      <c r="S97" s="7">
-        <v>1</v>
-      </c>
-      <c r="T97" s="13" t="s">
+      <c r="T97" s="7">
+        <v>1</v>
+      </c>
+      <c r="U97" s="13" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V97" s="13" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>141</v>
       </c>
@@ -6913,29 +7821,35 @@
         <v>0</v>
       </c>
       <c r="M98" s="10"/>
-      <c r="N98" s="7" t="s">
+      <c r="N98" t="s">
+        <v>252</v>
+      </c>
+      <c r="O98" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="O98" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="P98" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q98" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="Q98" s="8">
+      <c r="R98" s="8">
         <v>10</v>
       </c>
-      <c r="R98" s="7">
+      <c r="S98" s="7">
         <v>97</v>
       </c>
-      <c r="S98" s="7">
-        <v>1</v>
-      </c>
-      <c r="T98" s="13" t="s">
+      <c r="T98" s="7">
+        <v>1</v>
+      </c>
+      <c r="U98" s="13" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="V98" s="13" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" s="10"/>
       <c r="B99" s="17"/>
       <c r="C99" s="10"/>
@@ -6949,15 +7863,17 @@
       <c r="K99" s="11"/>
       <c r="L99" s="7"/>
       <c r="M99" s="10"/>
-      <c r="N99" s="7"/>
-      <c r="O99" s="10"/>
+      <c r="N99" s="10"/>
+      <c r="O99" s="7"/>
       <c r="P99" s="10"/>
-      <c r="Q99" s="7"/>
+      <c r="Q99" s="10"/>
       <c r="R99" s="7"/>
       <c r="S99" s="7"/>
-      <c r="T99" s="5"/>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T99" s="7"/>
+      <c r="U99" s="5"/>
+      <c r="V99" s="5"/>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A100" s="10"/>
       <c r="B100" s="17"/>
       <c r="C100" s="10"/>
@@ -6971,15 +7887,18 @@
       <c r="K100" s="11"/>
       <c r="L100" s="7"/>
       <c r="M100" s="10"/>
-      <c r="N100" s="7"/>
-      <c r="O100" s="10"/>
+      <c r="N100" s="10"/>
+      <c r="O100" s="7"/>
       <c r="P100" s="10"/>
-      <c r="Q100" s="7"/>
+      <c r="Q100" s="10"/>
       <c r="R100" s="7"/>
       <c r="S100" s="7"/>
-      <c r="T100" s="5"/>
+      <c r="T100" s="7"/>
+      <c r="U100" s="5"/>
+      <c r="V100" s="5"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AA98" xr:uid="{D7600A1C-8D91-4C3A-A5DE-920816BE31C1}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
